--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484127_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484127_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5751</v>
+        <v>5.2723</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6033</v>
+        <v>4.3005</v>
       </c>
       <c r="F2" t="n">
         <v>0.9718</v>
@@ -610,10 +610,10 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0883</v>
+        <v>-0.3911</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0995</v>
+        <v>-0.4023</v>
       </c>
       <c r="U2" t="n">
         <v>0.0112</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0082</v>
+        <v>1.2528</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5023</v>
+        <v>1.8311</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4941</v>
+        <v>-0.5783</v>
       </c>
       <c r="G3" t="n">
         <v>1.3412</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3168</v>
+        <v>-0.0723</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4364</v>
+        <v>-0.1077</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1196</v>
+        <v>0.0354</v>
       </c>
       <c r="V3" t="n">
         <v>-1.2065</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3928</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4351</v>
+        <v>0.9112</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0423</v>
+        <v>-0.2948</v>
       </c>
       <c r="G4" t="n">
         <v>1.0676</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4008</v>
+        <v>-0.1772</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8671</v>
+        <v>-0.391</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4663</v>
+        <v>0.2138</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8692</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONTALVO PEREZ</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2902</v>
+        <v>-0.2135</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1999</v>
+        <v>0.0158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.2293</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3179</v>
+        <v>-1.1728</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1743</v>
+        <v>-0.5393</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.6335</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8767</v>
+        <v>0.2879</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.277</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0402</v>
+        <v>0.5648</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5588</v>
+        <v>-1.4607</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2574</v>
+        <v>-0.2623</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8162</v>
+        <v>-1.1983</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1518</v>
+        <v>-0.3103</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8106</v>
+        <v>-0.272</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3411</v>
+        <v>-0.0383</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9405</v>
+        <v>0.6745</v>
       </c>
       <c r="W5" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1049</v>
+        <v>-0.2573</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3492</v>
+        <v>-0.6553</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4542</v>
+        <v>0.3981</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1099</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2743</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3061</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0318</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.3373</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>A. MONTALVO PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4146</v>
+        <v>-0.5697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1067</v>
+        <v>-0.4916</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5213</v>
+        <v>-0.0781</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3555</v>
+        <v>-0.3179</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1861</v>
+        <v>-1.1743</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5416</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8703</v>
+        <v>-0.8767</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7498</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5148</v>
+        <v>0.5588</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9359</v>
+        <v>-0.2574</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4211</v>
+        <v>0.8162</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.579</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6025</v>
+        <v>0.2919</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0057</v>
+        <v>0.1191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5968</v>
+        <v>0.1728</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2065</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6428</v>
+        <v>-0.8088</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2733</v>
+        <v>-0.035</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3696</v>
+        <v>-0.7738</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1728</v>
+        <v>0.3555</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5393</v>
+        <v>-0.1861</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6335</v>
+        <v>0.5416</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2879</v>
+        <v>1.8703</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.277</v>
+        <v>1.7498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5648</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4607</v>
+        <v>-1.5148</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2623</v>
+        <v>-1.9359</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1983</v>
+        <v>0.4211</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5952</v>
+        <v>-2.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7397</v>
+        <v>0.2083</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5611</v>
+        <v>-0.136</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1786</v>
+        <v>0.3443</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6745</v>
+        <v>1.2065</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2832</v>
+        <v>-0.9046</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7565</v>
+        <v>-1.4901</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4732</v>
+        <v>0.5855</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3808</v>
@@ -1156,13 +1156,13 @@
         <v>0.5952</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2993</v>
+        <v>0.0794</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.238</v>
+        <v>0.0284</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8991</v>
+        <v>-1.7927</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1485</v>
+        <v>-2.551</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7506</v>
+        <v>0.7583</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0229</v>
+        <v>-0.8872</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4516</v>
+        <v>0.3928</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5713</v>
+        <v>-1.2801</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1688</v>
+        <v>-0.3968</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0859</v>
+        <v>1.719</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0829</v>
+        <v>-2.1158</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1918</v>
+        <v>-0.4905</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5376</v>
+        <v>-1.3262</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6542</v>
+        <v>0.8357</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.5952</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.3887</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.5871</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.0584</v>
+        <v>-0.6476</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1189</v>
+        <v>-0.4363</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0606</v>
+        <v>-0.2112</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2065</v>
+        <v>0.3373</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. NINOT PEDROSA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2704</v>
+        <v>-1.8818</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6927</v>
+        <v>-0.1032</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5778</v>
+        <v>-1.7786</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4294</v>
+        <v>-2.0229</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.708</v>
+        <v>-1.4516</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2786</v>
+        <v>-0.5713</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3324</v>
+        <v>0.1688</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6522</v>
+        <v>0.0859</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6802</v>
+        <v>0.0829</v>
       </c>
       <c r="M11" t="n">
-        <v>0.903</v>
+        <v>-2.1918</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0558</v>
+        <v>-1.5376</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9588</v>
+        <v>-0.6542</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6314</v>
+        <v>-0.0411</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6236</v>
+        <v>-0.0736</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0078</v>
+        <v>0.0325</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6789</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1873</v>
+        <v>-2.5952</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4125</v>
+        <v>-2.0107</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2252</v>
+        <v>-0.5845</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8872</v>
+        <v>-4.1365</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3928</v>
+        <v>-3.4266</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2801</v>
+        <v>-0.7099</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3968</v>
+        <v>-1.8743</v>
       </c>
       <c r="K12" t="n">
-        <v>1.719</v>
+        <v>-1.9546</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1158</v>
+        <v>0.0803</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4905</v>
+        <v>-2.2622</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3262</v>
+        <v>-1.472</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8357</v>
+        <v>-0.7902</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9838</v>
+        <v>-0.1984</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0422</v>
+        <v>-0.1133</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2979</v>
+        <v>-0.204</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7443</v>
+        <v>0.0906</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3373</v>
+        <v>0.266</v>
       </c>
       <c r="W12" t="n">
         <v>0.266</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>M. NINOT PEDROSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4273</v>
+        <v>-2.6894</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7305</v>
+        <v>-2.0554</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6967</v>
+        <v>-0.6339</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1365</v>
+        <v>-1.4294</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.4266</v>
+        <v>-1.708</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7099</v>
+        <v>0.2786</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8743</v>
+        <v>-2.3324</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9546</v>
+        <v>-1.6522</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0803</v>
+        <v>-0.6802</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2622</v>
+        <v>0.903</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.472</v>
+        <v>-0.0558</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7902</v>
+        <v>0.9588</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3887</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9454</v>
+        <v>0.2125</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9238</v>
+        <v>0.2608</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0216</v>
+        <v>-0.0483</v>
       </c>
       <c r="V13" t="n">
-        <v>0.266</v>
+        <v>-1.4724</v>
       </c>
       <c r="W13" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.7535</v>
+        <v>-4.5715</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.5159</v>
+        <v>-2.333699999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2377</v>
+        <v>-2.2376</v>
       </c>
       <c r="G14" t="n">
         <v>-5.0973</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.145999999999999</v>
+        <v>-9.146000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>4.048699999999999</v>
+        <v>4.0487</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3221</v>
+        <v>4.322099999999997</v>
       </c>
       <c r="K14" t="n">
         <v>3.8368</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4852999999999998</v>
+        <v>0.4853</v>
       </c>
       <c r="M14" t="n">
         <v>-9.419499999999999</v>
@@ -1537,7 +1537,7 @@
         <v>3.5634</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9759</v>
+        <v>2.975899999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-9.9192</v>
@@ -1546,10 +1546,10 @@
         <v>12.8953</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2309</v>
+        <v>-1.0487</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7967</v>
+        <v>-1.6146</v>
       </c>
       <c r="U14" t="n">
         <v>0.5659</v>
@@ -1561,7 +1561,7 @@
         <v>4.8782</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.2792</v>
+        <v>-6.279199999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2961</v>
+        <v>4.6362</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0405</v>
+        <v>3.2445</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2557</v>
+        <v>1.3917</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0917</v>
@@ -1624,13 +1624,13 @@
         <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6971000000000001</v>
+        <v>1.0372</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0452</v>
+        <v>0.1588</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.8784</v>
       </c>
       <c r="V15" t="n">
         <v>3.6907</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6524</v>
+        <v>3.5811</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5136</v>
+        <v>2.8876</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1388</v>
+        <v>0.6935</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9841</v>
+        <v>1.5202</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7747</v>
+        <v>1.0629</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7906</v>
+        <v>0.4573</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4204</v>
+        <v>2.0041</v>
       </c>
       <c r="K16" t="n">
-        <v>4.496</v>
+        <v>1.4368</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.0756</v>
+        <v>0.5674</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4363</v>
+        <v>-0.484</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.3739</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2851</v>
+        <v>-0.11</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5493</v>
+        <v>-0.1374</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3629</v>
+        <v>-0.323</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1864</v>
+        <v>0.1855</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.0713</v>
+        <v>1.2065</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1978</v>
+        <v>3.3625</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1734</v>
+        <v>2.0035</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0244</v>
+        <v>1.359</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5202</v>
+        <v>1.9841</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0629</v>
+        <v>3.7747</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4573</v>
+        <v>-1.7906</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0041</v>
+        <v>2.4204</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4368</v>
+        <v>4.496</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5674</v>
+        <v>-2.0756</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.484</v>
+        <v>-0.4363</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3739</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.11</v>
+        <v>0.2851</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9919</v>
+        <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5207</v>
+        <v>0.2593</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0372</v>
+        <v>-0.1473</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4836</v>
+        <v>0.4066</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2065</v>
+        <v>-0.0713</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4453</v>
+        <v>0.4233</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1157</v>
+        <v>1.71</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5610000000000001</v>
+        <v>-1.2867</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6649</v>
+        <v>1.8891</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1513</v>
+        <v>3.8299</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8162</v>
+        <v>-1.9408</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2971</v>
+        <v>3.1156</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2971</v>
+        <v>3.871</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.7554</v>
       </c>
       <c r="M18" t="n">
-        <v>0.962</v>
+        <v>-1.2265</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1458</v>
+        <v>-0.0412</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8162</v>
+        <v>-1.1853</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1933</v>
+        <v>0.3358</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1814</v>
+        <v>-0.2153</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0118</v>
+        <v>0.5511</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2948</v>
+        <v>0.089</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6956</v>
+        <v>-0.5238</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4009</v>
+        <v>0.6128</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7905</v>
+        <v>0.6649</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4134</v>
+        <v>-0.1513</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3771</v>
+        <v>0.8162</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.151</v>
+        <v>-0.2971</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2313</v>
+        <v>-0.2971</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6395</v>
+        <v>0.962</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1821</v>
+        <v>0.1458</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4574</v>
+        <v>0.8162</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1903</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5416</v>
+        <v>-0.163</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5645</v>
+        <v>-0.2267</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9771</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3373</v>
+        <v>-1.2065</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1352</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1199</v>
+        <v>-0.2867</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4073</v>
+        <v>-1.8233</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5272</v>
+        <v>1.5365</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3334</v>
+        <v>0.6173</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7409</v>
+        <v>-0.0253</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0742</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1215</v>
+        <v>0.3306</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3115</v>
+        <v>0.3682</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4331</v>
+        <v>-0.0376</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2118</v>
+        <v>0.2867</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5707</v>
+        <v>-0.3935</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6412</v>
+        <v>0.6802</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.3806</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1661</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7855</v>
+        <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4327</v>
+        <v>0.2862</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8164</v>
+        <v>-0.17</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6163</v>
+        <v>0.4562</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4012</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0639</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>P. BARBECHO GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2509</v>
+        <v>-0.5723</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1999</v>
+        <v>-0.7836</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4508</v>
+        <v>0.2112</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8891</v>
+        <v>1.1485</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8299</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9408</v>
+        <v>1.0728</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1156</v>
+        <v>1.0585</v>
       </c>
       <c r="K21" t="n">
-        <v>3.871</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7554</v>
+        <v>0.1205</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2265</v>
+        <v>0.09</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0412</v>
+        <v>-0.8623</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1853</v>
+        <v>0.9523</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3384</v>
+        <v>0.1601</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7254</v>
+        <v>-0.1757</v>
       </c>
       <c r="U21" t="n">
-        <v>0.387</v>
+        <v>0.3358</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-1.881</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X21" t="n">
         <v>-1.2065</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.8051</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0273</v>
+        <v>-3.0195</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3444</v>
+        <v>2.2144</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6173</v>
+        <v>-1.3334</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0253</v>
+        <v>0.7409</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6425999999999999</v>
+        <v>-2.0742</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3306</v>
+        <v>-0.1215</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3682</v>
+        <v>1.3115</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0376</v>
+        <v>-1.4331</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2867</v>
+        <v>-1.2118</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3935</v>
+        <v>-0.5707</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6802</v>
+        <v>-0.6412</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1903</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-4.1661</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7935</v>
+        <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.11</v>
+        <v>1.5077</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3741</v>
+        <v>0.2042</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2641</v>
+        <v>1.3035</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4012</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0639</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. BARBECHO GARCIA</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.471</v>
+        <v>-0.9261</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2937</v>
+        <v>0.6753</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1773</v>
+        <v>-1.6015</v>
       </c>
       <c r="G23" t="n">
-        <v>1.1485</v>
+        <v>-1.7905</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.4134</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0728</v>
+        <v>-1.3771</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0585</v>
+        <v>-0.151</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9379999999999999</v>
+        <v>-0.2313</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1205</v>
+        <v>0.0803</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09</v>
+        <v>-1.6395</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8623</v>
+        <v>-0.1821</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9523</v>
+        <v>-1.4574</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7385</v>
+        <v>1.3207</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6858</v>
+        <v>0.5442</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0527</v>
+        <v>0.7764</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.881</v>
+        <v>0.3373</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2065</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.848</v>
+        <v>-1.388</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5414</v>
+        <v>-2.1333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6934</v>
+        <v>0.7452</v>
       </c>
       <c r="G24" t="n">
         <v>0.4887</v>
@@ -2326,13 +2326,13 @@
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4756</v>
+        <v>-0.0156</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1479</v>
+        <v>0.1997</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8692</v>
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.7534</v>
+        <v>8.113899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2376</v>
+        <v>2.237399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>4.5159</v>
+        <v>5.876099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>5.097200000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>9.146099999999999</v>
+        <v>9.146100000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.048699999999999</v>
+        <v>-4.0487</v>
       </c>
       <c r="J25" t="n">
-        <v>9.4194</v>
+        <v>9.419399999999998</v>
       </c>
       <c r="K25" t="n">
         <v>12.9828</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.5634</v>
+        <v>-3.563400000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-4.3222</v>
@@ -2392,7 +2392,7 @@
         <v>-3.8371</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4851000000000003</v>
+        <v>-0.4850999999999999</v>
       </c>
       <c r="P25" t="n">
         <v>-2.9758</v>
@@ -2401,16 +2401,16 @@
         <v>-12.8949</v>
       </c>
       <c r="R25" t="n">
-        <v>9.919199999999998</v>
+        <v>9.9192</v>
       </c>
       <c r="S25" t="n">
-        <v>3.230799999999999</v>
+        <v>4.591</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5659999999999998</v>
+        <v>-0.5661</v>
       </c>
       <c r="U25" t="n">
-        <v>3.7967</v>
+        <v>5.156899999999999</v>
       </c>
       <c r="V25" t="n">
         <v>1.4012</v>
